--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Référence vers un ou plusieurs consentements donnés dans le cadre de la préadmission.</t>
+    <t>Consentement lié à la préadmission</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
+++ b/nmoreau/ig/StructureDefinition-preadmission-consent-fr-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
